--- a/result.xlsx
+++ b/result.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="20">
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="40">
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52">
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56">
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73">
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77">
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84">
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86">
@@ -2881,7 +2881,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89">
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98">
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101">
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103">
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>11</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="108">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111">
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112">
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114">
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="116">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118">
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124">
@@ -4225,7 +4225,7 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="137">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="138">
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="157">
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="167">
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="169">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172">
@@ -5233,7 +5233,7 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="173">
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="176">
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="186">
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="192">
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="197">
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="201">
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="205">
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="207">
@@ -6269,7 +6269,7 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210">
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="216">
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="221">
@@ -6605,7 +6605,7 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="222">
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>11</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="224">
@@ -7025,7 +7025,7 @@
         </is>
       </c>
       <c r="F236" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="237">
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="F240" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="241">
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="F241" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="242">
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="F247" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="248">
@@ -7417,7 +7417,7 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="251">
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="F265" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="266">
@@ -7921,7 +7921,7 @@
         </is>
       </c>
       <c r="F268" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="269">
@@ -8061,7 +8061,7 @@
         </is>
       </c>
       <c r="F273" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="274">
@@ -8285,7 +8285,7 @@
         </is>
       </c>
       <c r="F281" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="282">
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="F291" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="292">
@@ -8677,7 +8677,7 @@
         </is>
       </c>
       <c r="F295" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="296">
@@ -8761,7 +8761,7 @@
         </is>
       </c>
       <c r="F298" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="299">
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="F306" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="307">
@@ -9069,7 +9069,7 @@
         </is>
       </c>
       <c r="F309" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="310">
@@ -9405,7 +9405,7 @@
         </is>
       </c>
       <c r="F321" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="322">
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="F328" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="329">
@@ -9713,7 +9713,7 @@
         </is>
       </c>
       <c r="F332" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="333">
@@ -9797,7 +9797,7 @@
         </is>
       </c>
       <c r="F335" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="336">
@@ -9853,7 +9853,7 @@
         </is>
       </c>
       <c r="F337" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="338">
@@ -9909,7 +9909,7 @@
         </is>
       </c>
       <c r="F339" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="340">
@@ -9965,7 +9965,7 @@
         </is>
       </c>
       <c r="F341" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
@@ -10077,7 +10077,7 @@
         </is>
       </c>
       <c r="F345" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="346">
@@ -10189,7 +10189,7 @@
         </is>
       </c>
       <c r="F349" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="350">
@@ -10217,7 +10217,7 @@
         </is>
       </c>
       <c r="F350" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="351">
@@ -10301,7 +10301,7 @@
         </is>
       </c>
       <c r="F353" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="354">
@@ -10357,7 +10357,7 @@
         </is>
       </c>
       <c r="F355" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="356">
@@ -10525,7 +10525,7 @@
         </is>
       </c>
       <c r="F361" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="362">
@@ -10693,7 +10693,7 @@
         </is>
       </c>
       <c r="F367" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="368">
@@ -10805,7 +10805,7 @@
         </is>
       </c>
       <c r="F371" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="372">
@@ -10861,7 +10861,7 @@
         </is>
       </c>
       <c r="F373" t="n">
-        <v>8</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="374">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="F376" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="377">
@@ -11001,7 +11001,7 @@
         </is>
       </c>
       <c r="F378" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="379">
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="F382" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="383">
@@ -11141,7 +11141,7 @@
         </is>
       </c>
       <c r="F383" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="384">
@@ -11225,7 +11225,7 @@
         </is>
       </c>
       <c r="F386" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="387">
@@ -11253,7 +11253,7 @@
         </is>
       </c>
       <c r="F387" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="388">
@@ -11281,7 +11281,7 @@
         </is>
       </c>
       <c r="F388" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="F392" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="393">
@@ -11505,7 +11505,7 @@
         </is>
       </c>
       <c r="F396" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="397">
@@ -11645,7 +11645,7 @@
         </is>
       </c>
       <c r="F401" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="402">
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="F404" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="405">
@@ -11897,7 +11897,7 @@
         </is>
       </c>
       <c r="F410" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="411">
@@ -11925,7 +11925,7 @@
         </is>
       </c>
       <c r="F411" t="n">
-        <v>11</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="412">
@@ -11953,7 +11953,7 @@
         </is>
       </c>
       <c r="F412" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="413">
@@ -12149,7 +12149,7 @@
         </is>
       </c>
       <c r="F419" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="420">
@@ -12345,7 +12345,7 @@
         </is>
       </c>
       <c r="F426" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="427">
@@ -12429,7 +12429,7 @@
         </is>
       </c>
       <c r="F429" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="430">
@@ -12457,7 +12457,7 @@
         </is>
       </c>
       <c r="F430" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="431">
@@ -12681,7 +12681,7 @@
         </is>
       </c>
       <c r="F438" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="439">
@@ -12709,7 +12709,7 @@
         </is>
       </c>
       <c r="F439" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="440">
@@ -12765,7 +12765,7 @@
         </is>
       </c>
       <c r="F441" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="442">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="F442" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="443">
@@ -12961,7 +12961,7 @@
         </is>
       </c>
       <c r="F448" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="449">
@@ -13045,7 +13045,7 @@
         </is>
       </c>
       <c r="F451" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="452">
@@ -13129,7 +13129,7 @@
         </is>
       </c>
       <c r="F454" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="455">
@@ -13241,7 +13241,7 @@
         </is>
       </c>
       <c r="F458" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="459">
@@ -13297,7 +13297,7 @@
         </is>
       </c>
       <c r="F460" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="461">
@@ -13437,7 +13437,7 @@
         </is>
       </c>
       <c r="F465" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="466">
@@ -13633,7 +13633,7 @@
         </is>
       </c>
       <c r="F472" t="n">
-        <v>8</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="473">
@@ -13773,7 +13773,7 @@
         </is>
       </c>
       <c r="F477" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="478">
@@ -13801,7 +13801,7 @@
         </is>
       </c>
       <c r="F478" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="479">
@@ -13913,7 +13913,7 @@
         </is>
       </c>
       <c r="F482" t="n">
-        <v>8</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="483">
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="F487" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="488">
@@ -14081,7 +14081,7 @@
         </is>
       </c>
       <c r="F488" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="489">
@@ -14193,7 +14193,7 @@
         </is>
       </c>
       <c r="F492" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="493">
@@ -14417,7 +14417,7 @@
         </is>
       </c>
       <c r="F500" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="501">
@@ -14557,7 +14557,7 @@
         </is>
       </c>
       <c r="F505" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="506">
@@ -14781,7 +14781,7 @@
         </is>
       </c>
       <c r="F513" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="514">
@@ -14809,7 +14809,7 @@
         </is>
       </c>
       <c r="F514" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="515">
@@ -14977,7 +14977,7 @@
         </is>
       </c>
       <c r="F520" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="521">
@@ -15061,7 +15061,7 @@
         </is>
       </c>
       <c r="F523" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="524">
@@ -15117,7 +15117,7 @@
         </is>
       </c>
       <c r="F525" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="526">
@@ -15341,7 +15341,7 @@
         </is>
       </c>
       <c r="F533" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="534">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="F537" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="538">
@@ -15509,7 +15509,7 @@
         </is>
       </c>
       <c r="F539" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="540">
@@ -15565,7 +15565,7 @@
         </is>
       </c>
       <c r="F541" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="542">
@@ -15621,7 +15621,7 @@
         </is>
       </c>
       <c r="F543" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="544">
@@ -15873,7 +15873,7 @@
         </is>
       </c>
       <c r="F552" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="553">
@@ -16097,7 +16097,7 @@
         </is>
       </c>
       <c r="F560" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="561">
@@ -16125,7 +16125,7 @@
         </is>
       </c>
       <c r="F561" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="562">
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="F566" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="567">
@@ -16293,7 +16293,7 @@
         </is>
       </c>
       <c r="F567" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="568">
@@ -16349,7 +16349,7 @@
         </is>
       </c>
       <c r="F569" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="570">
@@ -16489,7 +16489,7 @@
         </is>
       </c>
       <c r="F574" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="575">
@@ -16517,7 +16517,7 @@
         </is>
       </c>
       <c r="F575" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="576">
@@ -16545,7 +16545,7 @@
         </is>
       </c>
       <c r="F576" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="577">
@@ -16741,7 +16741,7 @@
         </is>
       </c>
       <c r="F583" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="584">
@@ -17077,7 +17077,7 @@
         </is>
       </c>
       <c r="F595" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="596">
@@ -17329,7 +17329,7 @@
         </is>
       </c>
       <c r="F604" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="605">
@@ -17469,7 +17469,7 @@
         </is>
       </c>
       <c r="F609" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="610">
@@ -17581,7 +17581,7 @@
         </is>
       </c>
       <c r="F613" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="614">
@@ -17609,7 +17609,7 @@
         </is>
       </c>
       <c r="F614" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="615">
@@ -17665,7 +17665,7 @@
         </is>
       </c>
       <c r="F616" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="617">
@@ -17693,7 +17693,7 @@
         </is>
       </c>
       <c r="F617" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="618">
@@ -17833,7 +17833,7 @@
         </is>
       </c>
       <c r="F622" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="623">
@@ -17917,7 +17917,7 @@
         </is>
       </c>
       <c r="F625" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="626">
@@ -18001,7 +18001,7 @@
         </is>
       </c>
       <c r="F628" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="629">
@@ -18057,7 +18057,7 @@
         </is>
       </c>
       <c r="F630" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="631">
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="F633" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="634">
@@ -18169,7 +18169,7 @@
         </is>
       </c>
       <c r="F634" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="635">
@@ -18225,7 +18225,7 @@
         </is>
       </c>
       <c r="F636" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="637">
@@ -18449,7 +18449,7 @@
         </is>
       </c>
       <c r="F644" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="645">
@@ -18477,7 +18477,7 @@
         </is>
       </c>
       <c r="F645" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="646">
@@ -18505,7 +18505,7 @@
         </is>
       </c>
       <c r="F646" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="647">
@@ -18533,7 +18533,7 @@
         </is>
       </c>
       <c r="F647" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="648">
@@ -18589,7 +18589,7 @@
         </is>
       </c>
       <c r="F649" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="650">
@@ -18701,7 +18701,7 @@
         </is>
       </c>
       <c r="F653" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="654">
@@ -18841,7 +18841,7 @@
         </is>
       </c>
       <c r="F658" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="659">
@@ -19121,7 +19121,7 @@
         </is>
       </c>
       <c r="F668" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="669">
@@ -19149,7 +19149,7 @@
         </is>
       </c>
       <c r="F669" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="670">
@@ -19177,7 +19177,7 @@
         </is>
       </c>
       <c r="F670" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="671">
@@ -19289,7 +19289,7 @@
         </is>
       </c>
       <c r="F674" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="675">
@@ -19317,7 +19317,7 @@
         </is>
       </c>
       <c r="F675" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="676">
@@ -19793,7 +19793,7 @@
         </is>
       </c>
       <c r="F692" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="693">
@@ -19821,7 +19821,7 @@
         </is>
       </c>
       <c r="F693" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="694">
@@ -19849,7 +19849,7 @@
         </is>
       </c>
       <c r="F694" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="695">
@@ -19877,7 +19877,7 @@
         </is>
       </c>
       <c r="F695" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="696">
@@ -19905,7 +19905,7 @@
         </is>
       </c>
       <c r="F696" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="697">
@@ -19933,7 +19933,7 @@
         </is>
       </c>
       <c r="F697" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="698">
@@ -20017,7 +20017,7 @@
         </is>
       </c>
       <c r="F700" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="701">
@@ -20297,7 +20297,7 @@
         </is>
       </c>
       <c r="F710" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="711">
@@ -20465,7 +20465,7 @@
         </is>
       </c>
       <c r="F716" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="717">
@@ -20493,7 +20493,7 @@
         </is>
       </c>
       <c r="F717" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="718">
@@ -20717,7 +20717,7 @@
         </is>
       </c>
       <c r="F725" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="726">
@@ -20885,7 +20885,7 @@
         </is>
       </c>
       <c r="F731" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="732">
@@ -21025,7 +21025,7 @@
         </is>
       </c>
       <c r="F736" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="737">
@@ -21081,7 +21081,7 @@
         </is>
       </c>
       <c r="F738" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="739">
@@ -21193,7 +21193,7 @@
         </is>
       </c>
       <c r="F742" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="743">
@@ -21249,7 +21249,7 @@
         </is>
       </c>
       <c r="F744" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="745">
@@ -21277,7 +21277,7 @@
         </is>
       </c>
       <c r="F745" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="746">
@@ -21333,7 +21333,7 @@
         </is>
       </c>
       <c r="F747" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="748">
@@ -21529,7 +21529,7 @@
         </is>
       </c>
       <c r="F754" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="755">
@@ -21781,7 +21781,7 @@
         </is>
       </c>
       <c r="F763" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="764">
@@ -22089,7 +22089,7 @@
         </is>
       </c>
       <c r="F774" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="775">
@@ -22117,7 +22117,7 @@
         </is>
       </c>
       <c r="F775" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="776">
@@ -22565,7 +22565,7 @@
         </is>
       </c>
       <c r="F791" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="792">
@@ -22649,7 +22649,7 @@
         </is>
       </c>
       <c r="F794" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="795">
@@ -22733,7 +22733,7 @@
         </is>
       </c>
       <c r="F797" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="798">
@@ -22817,7 +22817,7 @@
         </is>
       </c>
       <c r="F800" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="801">
@@ -23041,7 +23041,7 @@
         </is>
       </c>
       <c r="F808" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="809">
@@ -23097,7 +23097,7 @@
         </is>
       </c>
       <c r="F810" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="811">
@@ -23237,7 +23237,7 @@
         </is>
       </c>
       <c r="F815" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="816">
@@ -23601,7 +23601,7 @@
         </is>
       </c>
       <c r="F828" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="829">
@@ -23769,7 +23769,7 @@
         </is>
       </c>
       <c r="F834" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="835">
@@ -23853,7 +23853,7 @@
         </is>
       </c>
       <c r="F837" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="838">
@@ -23881,7 +23881,7 @@
         </is>
       </c>
       <c r="F838" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="839">
@@ -23965,7 +23965,7 @@
         </is>
       </c>
       <c r="F841" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="842">
@@ -24021,7 +24021,7 @@
         </is>
       </c>
       <c r="F843" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="844">
@@ -24273,7 +24273,7 @@
         </is>
       </c>
       <c r="F852" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="853">
@@ -24469,7 +24469,7 @@
         </is>
       </c>
       <c r="F859" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="860">
@@ -24497,7 +24497,7 @@
         </is>
       </c>
       <c r="F860" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="861">
@@ -24525,7 +24525,7 @@
         </is>
       </c>
       <c r="F861" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="862">
@@ -24609,7 +24609,7 @@
         </is>
       </c>
       <c r="F864" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="865">
@@ -24721,7 +24721,7 @@
         </is>
       </c>
       <c r="F868" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="869">
@@ -24749,7 +24749,7 @@
         </is>
       </c>
       <c r="F869" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="870">
@@ -24889,7 +24889,7 @@
         </is>
       </c>
       <c r="F874" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="875">
@@ -25085,7 +25085,7 @@
         </is>
       </c>
       <c r="F881" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="882">
@@ -25113,7 +25113,7 @@
         </is>
       </c>
       <c r="F882" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="883">
@@ -25141,7 +25141,7 @@
         </is>
       </c>
       <c r="F883" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="884">
@@ -25449,7 +25449,7 @@
         </is>
       </c>
       <c r="F894" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="895">
@@ -25505,7 +25505,7 @@
         </is>
       </c>
       <c r="F896" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="897">
@@ -25701,7 +25701,7 @@
         </is>
       </c>
       <c r="F903" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="904">
@@ -25897,7 +25897,7 @@
         </is>
       </c>
       <c r="F910" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="911">
@@ -26037,7 +26037,7 @@
         </is>
       </c>
       <c r="F915" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="916">
@@ -26205,7 +26205,7 @@
         </is>
       </c>
       <c r="F921" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="922">
@@ -26429,7 +26429,7 @@
         </is>
       </c>
       <c r="F929" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="930">
@@ -26653,7 +26653,7 @@
         </is>
       </c>
       <c r="F937" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="938">
@@ -26821,7 +26821,7 @@
         </is>
       </c>
       <c r="F943" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="944">
@@ -26877,7 +26877,7 @@
         </is>
       </c>
       <c r="F945" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="946">
@@ -26961,7 +26961,7 @@
         </is>
       </c>
       <c r="F948" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="949">
@@ -27241,7 +27241,7 @@
         </is>
       </c>
       <c r="F958" t="n">
-        <v>8</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="959">
@@ -27689,7 +27689,7 @@
         </is>
       </c>
       <c r="F974" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="975">
@@ -27857,7 +27857,7 @@
         </is>
       </c>
       <c r="F980" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="981">
@@ -27913,7 +27913,7 @@
         </is>
       </c>
       <c r="F982" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="983">
@@ -27941,7 +27941,7 @@
         </is>
       </c>
       <c r="F983" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="984">
@@ -28277,7 +28277,7 @@
         </is>
       </c>
       <c r="F995" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="996">
@@ -28305,7 +28305,7 @@
         </is>
       </c>
       <c r="F996" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="997">
@@ -28333,7 +28333,7 @@
         </is>
       </c>
       <c r="F997" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="998">

--- a/result.xlsx
+++ b/result.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>-1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="25">
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34">
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="35">
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40">
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="45">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="56">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="61">
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
     </row>
     <row r="62">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>-1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="64">
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>-1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="68">
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="71">
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>-1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="74">
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>8</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="77">
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="84">
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86">
@@ -2881,7 +2881,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="89">
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>-1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="90">
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="98">
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="101">
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="103">
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>-1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="104">
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="106">
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>-1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="108">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="109">
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="110">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="111">
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112">
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="114">
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="116">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="118">
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="124">
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="125">
@@ -4225,7 +4225,7 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="137">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="138">
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="157">
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>-1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="166">
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="167">
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172">
@@ -5233,7 +5233,7 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="173">
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="176">
@@ -5569,7 +5569,7 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>-1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="185">
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="186">
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>-1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="189">
@@ -5709,7 +5709,7 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="190">
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192">
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>-1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="193">
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="197">
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="201">
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="205">
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="207">
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="216">
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="221">
@@ -6605,7 +6605,7 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="222">
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>-1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="224">
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>-1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="225">
@@ -7025,7 +7025,7 @@
         </is>
       </c>
       <c r="F236" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="237">
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="F240" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="241">
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="F241" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="242">
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="F247" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="248">
@@ -7417,7 +7417,7 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="251">
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="F265" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="266">
@@ -7865,7 +7865,7 @@
         </is>
       </c>
       <c r="F266" t="n">
-        <v>-1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="267">
@@ -7921,7 +7921,7 @@
         </is>
       </c>
       <c r="F268" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="269">
@@ -8061,7 +8061,7 @@
         </is>
       </c>
       <c r="F273" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="274">
@@ -8285,7 +8285,7 @@
         </is>
       </c>
       <c r="F281" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="282">
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="F291" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="292">
@@ -8649,7 +8649,7 @@
         </is>
       </c>
       <c r="F294" t="n">
-        <v>-1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="295">
@@ -8761,7 +8761,7 @@
         </is>
       </c>
       <c r="F298" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="299">
@@ -8789,7 +8789,7 @@
         </is>
       </c>
       <c r="F299" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="300">
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="F302" t="n">
-        <v>-1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="303">
@@ -8901,7 +8901,7 @@
         </is>
       </c>
       <c r="F303" t="n">
-        <v>-1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="304">
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="F306" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="307">
@@ -9069,7 +9069,7 @@
         </is>
       </c>
       <c r="F309" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="310">
@@ -9405,7 +9405,7 @@
         </is>
       </c>
       <c r="F321" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="322">
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="F323" t="n">
-        <v>-1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="324">
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="F328" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="329">
@@ -9713,7 +9713,7 @@
         </is>
       </c>
       <c r="F332" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="333">
@@ -9797,7 +9797,7 @@
         </is>
       </c>
       <c r="F335" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="336">
@@ -9909,7 +9909,7 @@
         </is>
       </c>
       <c r="F339" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="340">
@@ -9993,7 +9993,7 @@
         </is>
       </c>
       <c r="F342" t="n">
-        <v>-1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="343">
@@ -10077,7 +10077,7 @@
         </is>
       </c>
       <c r="F345" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
     </row>
     <row r="346">
@@ -10189,7 +10189,7 @@
         </is>
       </c>
       <c r="F349" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="350">
@@ -10217,7 +10217,7 @@
         </is>
       </c>
       <c r="F350" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="351">
@@ -10357,7 +10357,7 @@
         </is>
       </c>
       <c r="F355" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="356">
@@ -10385,7 +10385,7 @@
         </is>
       </c>
       <c r="F356" t="n">
-        <v>-1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="357">
@@ -10525,7 +10525,7 @@
         </is>
       </c>
       <c r="F361" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="362">
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="F363" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="364">
@@ -10693,7 +10693,7 @@
         </is>
       </c>
       <c r="F367" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="368">
@@ -10805,7 +10805,7 @@
         </is>
       </c>
       <c r="F371" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="372">
@@ -10861,7 +10861,7 @@
         </is>
       </c>
       <c r="F373" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="374">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="F376" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="377">
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="F382" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="383">
@@ -11141,7 +11141,7 @@
         </is>
       </c>
       <c r="F383" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="384">
@@ -11225,7 +11225,7 @@
         </is>
       </c>
       <c r="F386" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="387">
@@ -11253,7 +11253,7 @@
         </is>
       </c>
       <c r="F387" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="388">
@@ -11505,7 +11505,7 @@
         </is>
       </c>
       <c r="F396" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="397">
@@ -11533,7 +11533,7 @@
         </is>
       </c>
       <c r="F397" t="n">
-        <v>-1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="398">
@@ -11645,7 +11645,7 @@
         </is>
       </c>
       <c r="F401" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="402">
@@ -11701,7 +11701,7 @@
         </is>
       </c>
       <c r="F403" t="n">
-        <v>-1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="404">
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="F404" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="405">
@@ -11897,7 +11897,7 @@
         </is>
       </c>
       <c r="F410" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="411">
@@ -11925,7 +11925,7 @@
         </is>
       </c>
       <c r="F411" t="n">
-        <v>-1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="412">
@@ -11953,7 +11953,7 @@
         </is>
       </c>
       <c r="F412" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="413">
@@ -12149,7 +12149,7 @@
         </is>
       </c>
       <c r="F419" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="420">
@@ -12345,7 +12345,7 @@
         </is>
       </c>
       <c r="F426" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="427">
@@ -12429,7 +12429,7 @@
         </is>
       </c>
       <c r="F429" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="430">
@@ -12457,7 +12457,7 @@
         </is>
       </c>
       <c r="F430" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="431">
@@ -12681,7 +12681,7 @@
         </is>
       </c>
       <c r="F438" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="439">
@@ -12709,7 +12709,7 @@
         </is>
       </c>
       <c r="F439" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="440">
@@ -12765,7 +12765,7 @@
         </is>
       </c>
       <c r="F441" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="442">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="F442" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="443">
@@ -12961,7 +12961,7 @@
         </is>
       </c>
       <c r="F448" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="449">
@@ -13045,7 +13045,7 @@
         </is>
       </c>
       <c r="F451" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="452">
@@ -13129,7 +13129,7 @@
         </is>
       </c>
       <c r="F454" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="455">
@@ -13241,7 +13241,7 @@
         </is>
       </c>
       <c r="F458" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="459">
@@ -13269,7 +13269,7 @@
         </is>
       </c>
       <c r="F459" t="n">
-        <v>-1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="460">
@@ -13297,7 +13297,7 @@
         </is>
       </c>
       <c r="F460" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="461">
@@ -13437,7 +13437,7 @@
         </is>
       </c>
       <c r="F465" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="466">
@@ -13465,7 +13465,7 @@
         </is>
       </c>
       <c r="F466" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="467">
@@ -13633,7 +13633,7 @@
         </is>
       </c>
       <c r="F472" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="473">
@@ -13689,7 +13689,7 @@
         </is>
       </c>
       <c r="F474" t="n">
-        <v>-1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="475">
@@ -13773,7 +13773,7 @@
         </is>
       </c>
       <c r="F477" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="478">
@@ -13801,7 +13801,7 @@
         </is>
       </c>
       <c r="F478" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="479">
@@ -13913,7 +13913,7 @@
         </is>
       </c>
       <c r="F482" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="483">
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="F487" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="488">
@@ -14081,7 +14081,7 @@
         </is>
       </c>
       <c r="F488" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="489">
@@ -14193,7 +14193,7 @@
         </is>
       </c>
       <c r="F492" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="493">
@@ -14249,7 +14249,7 @@
         </is>
       </c>
       <c r="F494" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="495">
@@ -14417,7 +14417,7 @@
         </is>
       </c>
       <c r="F500" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="501">
@@ -14557,7 +14557,7 @@
         </is>
       </c>
       <c r="F505" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="506">
@@ -14781,7 +14781,7 @@
         </is>
       </c>
       <c r="F513" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="514">
@@ -14977,7 +14977,7 @@
         </is>
       </c>
       <c r="F520" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="521">
@@ -15061,7 +15061,7 @@
         </is>
       </c>
       <c r="F523" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="524">
@@ -15117,7 +15117,7 @@
         </is>
       </c>
       <c r="F525" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="526">
@@ -15257,7 +15257,7 @@
         </is>
       </c>
       <c r="F530" t="n">
-        <v>-1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="531">
@@ -15341,7 +15341,7 @@
         </is>
       </c>
       <c r="F533" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="534">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="F537" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="538">
@@ -15509,7 +15509,7 @@
         </is>
       </c>
       <c r="F539" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="540">
@@ -15537,7 +15537,7 @@
         </is>
       </c>
       <c r="F540" t="n">
-        <v>-1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="541">
@@ -15565,7 +15565,7 @@
         </is>
       </c>
       <c r="F541" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="542">
@@ -15621,7 +15621,7 @@
         </is>
       </c>
       <c r="F543" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="544">
@@ -15873,7 +15873,7 @@
         </is>
       </c>
       <c r="F552" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="553">
@@ -15929,7 +15929,7 @@
         </is>
       </c>
       <c r="F554" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="555">
@@ -16097,7 +16097,7 @@
         </is>
       </c>
       <c r="F560" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="561">
@@ -16125,7 +16125,7 @@
         </is>
       </c>
       <c r="F561" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="562">
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="F566" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="567">
@@ -16293,7 +16293,7 @@
         </is>
       </c>
       <c r="F567" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="568">
@@ -16349,7 +16349,7 @@
         </is>
       </c>
       <c r="F569" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="570">
@@ -16377,7 +16377,7 @@
         </is>
       </c>
       <c r="F570" t="n">
-        <v>-1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="571">
@@ -16489,7 +16489,7 @@
         </is>
       </c>
       <c r="F574" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="575">
@@ -16517,7 +16517,7 @@
         </is>
       </c>
       <c r="F575" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="576">
@@ -16545,7 +16545,7 @@
         </is>
       </c>
       <c r="F576" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="577">
@@ -16685,7 +16685,7 @@
         </is>
       </c>
       <c r="F581" t="n">
-        <v>-1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="582">
@@ -16741,7 +16741,7 @@
         </is>
       </c>
       <c r="F583" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="584">
@@ -17077,7 +17077,7 @@
         </is>
       </c>
       <c r="F595" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="596">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="F598" t="n">
-        <v>-1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="599">
@@ -17329,7 +17329,7 @@
         </is>
       </c>
       <c r="F604" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="605">
@@ -17469,7 +17469,7 @@
         </is>
       </c>
       <c r="F609" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="610">
@@ -17525,7 +17525,7 @@
         </is>
       </c>
       <c r="F611" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="612">
@@ -17581,7 +17581,7 @@
         </is>
       </c>
       <c r="F613" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="614">
@@ -17609,7 +17609,7 @@
         </is>
       </c>
       <c r="F614" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="615">
@@ -17665,7 +17665,7 @@
         </is>
       </c>
       <c r="F616" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="617">
@@ -17693,7 +17693,7 @@
         </is>
       </c>
       <c r="F617" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="618">
@@ -17917,7 +17917,7 @@
         </is>
       </c>
       <c r="F625" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="626">
@@ -18001,7 +18001,7 @@
         </is>
       </c>
       <c r="F628" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="629">
@@ -18057,7 +18057,7 @@
         </is>
       </c>
       <c r="F630" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="631">
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="F633" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="634">
@@ -18169,7 +18169,7 @@
         </is>
       </c>
       <c r="F634" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="635">
@@ -18225,7 +18225,7 @@
         </is>
       </c>
       <c r="F636" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="637">
@@ -18393,7 +18393,7 @@
         </is>
       </c>
       <c r="F642" t="n">
-        <v>-1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="643">
@@ -18449,7 +18449,7 @@
         </is>
       </c>
       <c r="F644" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="645">
@@ -18477,7 +18477,7 @@
         </is>
       </c>
       <c r="F645" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="646">
@@ -18505,7 +18505,7 @@
         </is>
       </c>
       <c r="F646" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="647">
@@ -18533,7 +18533,7 @@
         </is>
       </c>
       <c r="F647" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="648">
@@ -18589,7 +18589,7 @@
         </is>
       </c>
       <c r="F649" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="650">
@@ -18617,7 +18617,7 @@
         </is>
       </c>
       <c r="F650" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="651">
@@ -18701,7 +18701,7 @@
         </is>
       </c>
       <c r="F653" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="654">
@@ -18757,7 +18757,7 @@
         </is>
       </c>
       <c r="F655" t="n">
-        <v>-1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="656">
@@ -18841,7 +18841,7 @@
         </is>
       </c>
       <c r="F658" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="659">
@@ -18925,7 +18925,7 @@
         </is>
       </c>
       <c r="F661" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="662">
@@ -19121,7 +19121,7 @@
         </is>
       </c>
       <c r="F668" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="669">
@@ -19149,7 +19149,7 @@
         </is>
       </c>
       <c r="F669" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="670">
@@ -19177,7 +19177,7 @@
         </is>
       </c>
       <c r="F670" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="671">
@@ -19289,7 +19289,7 @@
         </is>
       </c>
       <c r="F674" t="n">
-        <v>10</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="675">
@@ -19317,7 +19317,7 @@
         </is>
       </c>
       <c r="F675" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="676">
@@ -19793,7 +19793,7 @@
         </is>
       </c>
       <c r="F692" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="693">
@@ -19821,7 +19821,7 @@
         </is>
       </c>
       <c r="F693" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="694">
@@ -19849,7 +19849,7 @@
         </is>
       </c>
       <c r="F694" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="695">
@@ -19877,7 +19877,7 @@
         </is>
       </c>
       <c r="F695" t="n">
-        <v>10</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="696">
@@ -19905,7 +19905,7 @@
         </is>
       </c>
       <c r="F696" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="697">
@@ -19933,7 +19933,7 @@
         </is>
       </c>
       <c r="F697" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="698">
@@ -20129,7 +20129,7 @@
         </is>
       </c>
       <c r="F704" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="705">
@@ -20213,7 +20213,7 @@
         </is>
       </c>
       <c r="F707" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="708">
@@ -20297,7 +20297,7 @@
         </is>
       </c>
       <c r="F710" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="711">
@@ -20465,7 +20465,7 @@
         </is>
       </c>
       <c r="F716" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="717">
@@ -20493,7 +20493,7 @@
         </is>
       </c>
       <c r="F717" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="718">
@@ -20605,7 +20605,7 @@
         </is>
       </c>
       <c r="F721" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="722">
@@ -20717,7 +20717,7 @@
         </is>
       </c>
       <c r="F725" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="726">
@@ -20745,7 +20745,7 @@
         </is>
       </c>
       <c r="F726" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="727">
@@ -20885,7 +20885,7 @@
         </is>
       </c>
       <c r="F731" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="732">
@@ -21025,7 +21025,7 @@
         </is>
       </c>
       <c r="F736" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="737">
@@ -21081,7 +21081,7 @@
         </is>
       </c>
       <c r="F738" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="739">
@@ -21193,7 +21193,7 @@
         </is>
       </c>
       <c r="F742" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="743">
@@ -21249,7 +21249,7 @@
         </is>
       </c>
       <c r="F744" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="745">
@@ -21277,7 +21277,7 @@
         </is>
       </c>
       <c r="F745" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="746">
@@ -21333,7 +21333,7 @@
         </is>
       </c>
       <c r="F747" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="748">
@@ -21417,7 +21417,7 @@
         </is>
       </c>
       <c r="F750" t="n">
-        <v>-1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="751">
@@ -21529,7 +21529,7 @@
         </is>
       </c>
       <c r="F754" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="755">
@@ -21781,7 +21781,7 @@
         </is>
       </c>
       <c r="F763" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="764">
@@ -22089,7 +22089,7 @@
         </is>
       </c>
       <c r="F774" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="775">
@@ -22117,7 +22117,7 @@
         </is>
       </c>
       <c r="F775" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="776">
@@ -22285,7 +22285,7 @@
         </is>
       </c>
       <c r="F781" t="n">
-        <v>-1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="782">
@@ -22313,7 +22313,7 @@
         </is>
       </c>
       <c r="F782" t="n">
-        <v>-1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="783">
@@ -22537,7 +22537,7 @@
         </is>
       </c>
       <c r="F790" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="791">
@@ -22565,7 +22565,7 @@
         </is>
       </c>
       <c r="F791" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="792">
@@ -22649,7 +22649,7 @@
         </is>
       </c>
       <c r="F794" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="795">
@@ -22733,7 +22733,7 @@
         </is>
       </c>
       <c r="F797" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="798">
@@ -22817,7 +22817,7 @@
         </is>
       </c>
       <c r="F800" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="801">
@@ -22845,7 +22845,7 @@
         </is>
       </c>
       <c r="F801" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="802">
@@ -23041,7 +23041,7 @@
         </is>
       </c>
       <c r="F808" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="809">
@@ -23097,7 +23097,7 @@
         </is>
       </c>
       <c r="F810" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="811">
@@ -23237,7 +23237,7 @@
         </is>
       </c>
       <c r="F815" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="816">
@@ -23601,7 +23601,7 @@
         </is>
       </c>
       <c r="F828" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="829">
@@ -23769,7 +23769,7 @@
         </is>
       </c>
       <c r="F834" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="835">
@@ -23797,7 +23797,7 @@
         </is>
       </c>
       <c r="F835" t="n">
-        <v>-1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="836">
@@ -23853,7 +23853,7 @@
         </is>
       </c>
       <c r="F837" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="838">
@@ -23881,7 +23881,7 @@
         </is>
       </c>
       <c r="F838" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="839">
@@ -23965,7 +23965,7 @@
         </is>
       </c>
       <c r="F841" t="n">
-        <v>10</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="842">
@@ -24021,7 +24021,7 @@
         </is>
       </c>
       <c r="F843" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="844">
@@ -24273,7 +24273,7 @@
         </is>
       </c>
       <c r="F852" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="853">
@@ -24385,7 +24385,7 @@
         </is>
       </c>
       <c r="F856" t="n">
-        <v>-1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="857">
@@ -24469,7 +24469,7 @@
         </is>
       </c>
       <c r="F859" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="860">
@@ -24497,7 +24497,7 @@
         </is>
       </c>
       <c r="F860" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="861">
@@ -24525,7 +24525,7 @@
         </is>
       </c>
       <c r="F861" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="862">
@@ -24609,7 +24609,7 @@
         </is>
       </c>
       <c r="F864" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="865">
@@ -24721,7 +24721,7 @@
         </is>
       </c>
       <c r="F868" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="869">
@@ -24749,7 +24749,7 @@
         </is>
       </c>
       <c r="F869" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="870">
@@ -24889,7 +24889,7 @@
         </is>
       </c>
       <c r="F874" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="875">
@@ -25057,7 +25057,7 @@
         </is>
       </c>
       <c r="F880" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="881">
@@ -25085,7 +25085,7 @@
         </is>
       </c>
       <c r="F881" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="882">
@@ -25113,7 +25113,7 @@
         </is>
       </c>
       <c r="F882" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="883">
@@ -25141,7 +25141,7 @@
         </is>
       </c>
       <c r="F883" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="884">
@@ -25309,7 +25309,7 @@
         </is>
       </c>
       <c r="F889" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="890">
@@ -25449,7 +25449,7 @@
         </is>
       </c>
       <c r="F894" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="895">
@@ -25505,7 +25505,7 @@
         </is>
       </c>
       <c r="F896" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="897">
@@ -25561,7 +25561,7 @@
         </is>
       </c>
       <c r="F898" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="899">
@@ -25701,7 +25701,7 @@
         </is>
       </c>
       <c r="F903" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="904">
@@ -25757,7 +25757,7 @@
         </is>
       </c>
       <c r="F905" t="n">
-        <v>-1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="906">
@@ -25785,7 +25785,7 @@
         </is>
       </c>
       <c r="F906" t="n">
-        <v>-1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="907">
@@ -25897,7 +25897,7 @@
         </is>
       </c>
       <c r="F910" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="911">
@@ -26037,7 +26037,7 @@
         </is>
       </c>
       <c r="F915" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="916">
@@ -26205,7 +26205,7 @@
         </is>
       </c>
       <c r="F921" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="922">
@@ -26345,7 +26345,7 @@
         </is>
       </c>
       <c r="F926" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="927">
@@ -26429,7 +26429,7 @@
         </is>
       </c>
       <c r="F929" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="930">
@@ -26597,7 +26597,7 @@
         </is>
       </c>
       <c r="F935" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="936">
@@ -26653,7 +26653,7 @@
         </is>
       </c>
       <c r="F937" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="938">
@@ -26793,7 +26793,7 @@
         </is>
       </c>
       <c r="F942" t="n">
-        <v>-1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="943">
@@ -26821,7 +26821,7 @@
         </is>
       </c>
       <c r="F943" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="944">
@@ -26877,7 +26877,7 @@
         </is>
       </c>
       <c r="F945" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="946">
@@ -26961,7 +26961,7 @@
         </is>
       </c>
       <c r="F948" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="949">
@@ -27213,7 +27213,7 @@
         </is>
       </c>
       <c r="F957" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="958">
@@ -27241,7 +27241,7 @@
         </is>
       </c>
       <c r="F958" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="959">
@@ -27297,7 +27297,7 @@
         </is>
       </c>
       <c r="F960" t="n">
-        <v>-1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="961">
@@ -27689,7 +27689,7 @@
         </is>
       </c>
       <c r="F974" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="975">
@@ -27857,7 +27857,7 @@
         </is>
       </c>
       <c r="F980" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="981">
@@ -27913,7 +27913,7 @@
         </is>
       </c>
       <c r="F982" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="983">
@@ -27941,7 +27941,7 @@
         </is>
       </c>
       <c r="F983" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="984">
@@ -28277,7 +28277,7 @@
         </is>
       </c>
       <c r="F995" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="996">
@@ -28305,7 +28305,7 @@
         </is>
       </c>
       <c r="F996" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="997">
@@ -28333,7 +28333,7 @@
         </is>
       </c>
       <c r="F997" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="998">

--- a/result.xlsx
+++ b/result.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>-1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>-1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>-1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>-1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>-1</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24">
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>-1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25">
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1173,7 +1173,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44">
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49">
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>-1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="67">
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>-1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70">
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72">
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79">
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>-1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="82">
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87">
@@ -2881,7 +2881,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90">
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>-1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="91">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96">
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>40</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="104">
@@ -3329,7 +3329,7 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="107">
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="108">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116">
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118">
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="120">
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
@@ -3805,7 +3805,7 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="122">
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="123">
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125">
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="126">
@@ -3945,7 +3945,7 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>-1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="127">
@@ -3973,7 +3973,7 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="128">
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="129">
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -4057,7 +4057,7 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="135">
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
@@ -4225,7 +4225,7 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139">
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="140">
@@ -4337,7 +4337,7 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>-1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="142">
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="144">
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -4589,7 +4589,7 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>-1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="152">
@@ -4673,7 +4673,7 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="153">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="154">
@@ -4729,7 +4729,7 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="166">
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167">
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168">
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="170">
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="171">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
@@ -5233,7 +5233,7 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -5345,7 +5345,7 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="177">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>-1</v>
+        <v>41</v>
       </c>
     </row>
     <row r="179">
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -5457,7 +5457,7 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="181">
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>-1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="182">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>-1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="183">
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -5569,7 +5569,7 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="185">
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>-1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="187">
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -5709,7 +5709,7 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="190">
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193">
@@ -5821,7 +5821,7 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="194">
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195">
@@ -5877,7 +5877,7 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>-1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="196">
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197">
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198">
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>-1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="200">
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201">
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="202">
@@ -6073,7 +6073,7 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203">
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205">
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="206">
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="207">
@@ -6241,7 +6241,7 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>-1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="209">
@@ -6269,7 +6269,7 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="212">
@@ -6353,7 +6353,7 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213">
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="214">
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="216">
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="217">
@@ -6493,7 +6493,7 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -6605,7 +6605,7 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="224">
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="225">
@@ -6717,7 +6717,7 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>-1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="226">
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="227">
@@ -6773,7 +6773,7 @@
         </is>
       </c>
       <c r="F227" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="228">
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="229">
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="F229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="F233" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234">
@@ -7025,7 +7025,7 @@
         </is>
       </c>
       <c r="F236" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="F237" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238">
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="F240" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="F241" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="F242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -7221,7 +7221,7 @@
         </is>
       </c>
       <c r="F243" t="n">
-        <v>-1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="244">
@@ -7249,7 +7249,7 @@
         </is>
       </c>
       <c r="F244" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
@@ -7277,7 +7277,7 @@
         </is>
       </c>
       <c r="F245" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="F246" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="247">
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="F247" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="248">
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="F248" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="249">
@@ -7389,7 +7389,7 @@
         </is>
       </c>
       <c r="F249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -7417,7 +7417,7 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="F251" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252">
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="F252" t="n">
-        <v>-1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="253">
@@ -7501,7 +7501,7 @@
         </is>
       </c>
       <c r="F253" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -7529,7 +7529,7 @@
         </is>
       </c>
       <c r="F254" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="255">
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="F255" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -7585,7 +7585,7 @@
         </is>
       </c>
       <c r="F256" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="257">
@@ -7697,7 +7697,7 @@
         </is>
       </c>
       <c r="F260" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261">
@@ -7725,7 +7725,7 @@
         </is>
       </c>
       <c r="F261" t="n">
-        <v>-1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="262">
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="F265" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="266">
@@ -7865,7 +7865,7 @@
         </is>
       </c>
       <c r="F266" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267">
@@ -7921,7 +7921,7 @@
         </is>
       </c>
       <c r="F268" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269">
@@ -7977,7 +7977,7 @@
         </is>
       </c>
       <c r="F270" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271">
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c r="F271" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272">
@@ -8033,7 +8033,7 @@
         </is>
       </c>
       <c r="F272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -8061,7 +8061,7 @@
         </is>
       </c>
       <c r="F273" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="274">
@@ -8117,7 +8117,7 @@
         </is>
       </c>
       <c r="F275" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="276">
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="F276" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277">
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="F278" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="279">
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="F280" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="281">
@@ -8285,7 +8285,7 @@
         </is>
       </c>
       <c r="F281" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282">
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="F283" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284">
@@ -8369,7 +8369,7 @@
         </is>
       </c>
       <c r="F284" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="285">
@@ -8397,7 +8397,7 @@
         </is>
       </c>
       <c r="F285" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="286">
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="F287" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="288">
@@ -8481,7 +8481,7 @@
         </is>
       </c>
       <c r="F288" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="289">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="F289" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="290">
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="F290" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291">
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="F291" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="F293" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="294">
@@ -8649,7 +8649,7 @@
         </is>
       </c>
       <c r="F294" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="295">
@@ -8677,7 +8677,7 @@
         </is>
       </c>
       <c r="F295" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296">
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="F296" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="297">
@@ -8761,7 +8761,7 @@
         </is>
       </c>
       <c r="F298" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299">
@@ -8789,7 +8789,7 @@
         </is>
       </c>
       <c r="F299" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300">
@@ -8817,7 +8817,7 @@
         </is>
       </c>
       <c r="F300" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="301">
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="F302" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
@@ -8901,7 +8901,7 @@
         </is>
       </c>
       <c r="F303" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="304">
@@ -8929,7 +8929,7 @@
         </is>
       </c>
       <c r="F304" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="305">
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="F305" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="306">
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="F306" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="307">
@@ -9013,7 +9013,7 @@
         </is>
       </c>
       <c r="F307" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="308">
@@ -9041,7 +9041,7 @@
         </is>
       </c>
       <c r="F308" t="n">
-        <v>-1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="309">
@@ -9069,7 +9069,7 @@
         </is>
       </c>
       <c r="F309" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="310">
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="F310" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
@@ -9153,7 +9153,7 @@
         </is>
       </c>
       <c r="F312" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="F313" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="314">
@@ -9209,7 +9209,7 @@
         </is>
       </c>
       <c r="F314" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="315">
@@ -9237,7 +9237,7 @@
         </is>
       </c>
       <c r="F315" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="316">
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="F317" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318">
@@ -9321,7 +9321,7 @@
         </is>
       </c>
       <c r="F318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319">
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="F319" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="320">
@@ -9377,7 +9377,7 @@
         </is>
       </c>
       <c r="F320" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="321">
@@ -9405,7 +9405,7 @@
         </is>
       </c>
       <c r="F321" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="322">
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="F322" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323">
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="F323" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="324">
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="F324" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325">
@@ -9517,7 +9517,7 @@
         </is>
       </c>
       <c r="F325" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="326">
@@ -9573,7 +9573,7 @@
         </is>
       </c>
       <c r="F327" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="328">
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="F328" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="329">
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="F330" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="331">
@@ -9713,7 +9713,7 @@
         </is>
       </c>
       <c r="F332" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="333">
@@ -9741,7 +9741,7 @@
         </is>
       </c>
       <c r="F333" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -9769,7 +9769,7 @@
         </is>
       </c>
       <c r="F334" t="n">
-        <v>-1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="335">
@@ -9797,7 +9797,7 @@
         </is>
       </c>
       <c r="F335" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="336">
@@ -9825,7 +9825,7 @@
         </is>
       </c>
       <c r="F336" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337">
@@ -9853,7 +9853,7 @@
         </is>
       </c>
       <c r="F337" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338">
@@ -9881,7 +9881,7 @@
         </is>
       </c>
       <c r="F338" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="339">
@@ -9909,7 +9909,7 @@
         </is>
       </c>
       <c r="F339" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="340">
@@ -9937,7 +9937,7 @@
         </is>
       </c>
       <c r="F340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341">
@@ -9965,7 +9965,7 @@
         </is>
       </c>
       <c r="F341" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342">
@@ -9993,7 +9993,7 @@
         </is>
       </c>
       <c r="F342" t="n">
-        <v>40</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="343">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="F343" t="n">
-        <v>-1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="344">
@@ -10049,7 +10049,7 @@
         </is>
       </c>
       <c r="F344" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="345">
@@ -10077,7 +10077,7 @@
         </is>
       </c>
       <c r="F345" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="346">
@@ -10105,7 +10105,7 @@
         </is>
       </c>
       <c r="F346" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347">
@@ -10161,7 +10161,7 @@
         </is>
       </c>
       <c r="F348" t="n">
-        <v>-1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="349">
@@ -10189,7 +10189,7 @@
         </is>
       </c>
       <c r="F349" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="350">
@@ -10217,7 +10217,7 @@
         </is>
       </c>
       <c r="F350" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="351">
@@ -10273,7 +10273,7 @@
         </is>
       </c>
       <c r="F352" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="353">
@@ -10301,7 +10301,7 @@
         </is>
       </c>
       <c r="F353" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="354">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="F354" t="n">
-        <v>-1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="355">
@@ -10357,7 +10357,7 @@
         </is>
       </c>
       <c r="F355" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="356">
@@ -10385,7 +10385,7 @@
         </is>
       </c>
       <c r="F356" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357">
@@ -10413,7 +10413,7 @@
         </is>
       </c>
       <c r="F357" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
@@ -10441,7 +10441,7 @@
         </is>
       </c>
       <c r="F358" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="359">
@@ -10469,7 +10469,7 @@
         </is>
       </c>
       <c r="F359" t="n">
-        <v>-1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="360">
@@ -10497,7 +10497,7 @@
         </is>
       </c>
       <c r="F360" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="361">
@@ -10525,7 +10525,7 @@
         </is>
       </c>
       <c r="F361" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="362">
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="F363" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="364">
@@ -10665,7 +10665,7 @@
         </is>
       </c>
       <c r="F366" t="n">
-        <v>-1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="367">
@@ -10693,7 +10693,7 @@
         </is>
       </c>
       <c r="F367" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="368">
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="F368" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="369">
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="F369" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="370">
@@ -10805,7 +10805,7 @@
         </is>
       </c>
       <c r="F371" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="372">
@@ -10833,7 +10833,7 @@
         </is>
       </c>
       <c r="F372" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
@@ -10861,7 +10861,7 @@
         </is>
       </c>
       <c r="F373" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="374">
@@ -10889,7 +10889,7 @@
         </is>
       </c>
       <c r="F374" t="n">
-        <v>-1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="375">
@@ -10917,7 +10917,7 @@
         </is>
       </c>
       <c r="F375" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="376">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="F376" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="377">
@@ -10973,7 +10973,7 @@
         </is>
       </c>
       <c r="F377" t="n">
-        <v>-1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="378">
@@ -11001,7 +11001,7 @@
         </is>
       </c>
       <c r="F378" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="379">
@@ -11057,7 +11057,7 @@
         </is>
       </c>
       <c r="F380" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="381">
@@ -11085,7 +11085,7 @@
         </is>
       </c>
       <c r="F381" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="382">
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="F382" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="383">
@@ -11141,7 +11141,7 @@
         </is>
       </c>
       <c r="F383" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="384">
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="F384" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="385">
@@ -11197,7 +11197,7 @@
         </is>
       </c>
       <c r="F385" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="386">
@@ -11225,7 +11225,7 @@
         </is>
       </c>
       <c r="F386" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="387">
@@ -11253,7 +11253,7 @@
         </is>
       </c>
       <c r="F387" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="388">
@@ -11281,7 +11281,7 @@
         </is>
       </c>
       <c r="F388" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="389">
@@ -11309,7 +11309,7 @@
         </is>
       </c>
       <c r="F389" t="n">
-        <v>-1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="390">
@@ -11365,7 +11365,7 @@
         </is>
       </c>
       <c r="F391" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="392">
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="F392" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="393">
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="F395" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="396">
@@ -11505,7 +11505,7 @@
         </is>
       </c>
       <c r="F396" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="397">
@@ -11533,7 +11533,7 @@
         </is>
       </c>
       <c r="F397" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="398">
@@ -11561,7 +11561,7 @@
         </is>
       </c>
       <c r="F398" t="n">
-        <v>-1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="399">
@@ -11589,7 +11589,7 @@
         </is>
       </c>
       <c r="F399" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="400">
@@ -11645,7 +11645,7 @@
         </is>
       </c>
       <c r="F401" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="402">
@@ -11673,7 +11673,7 @@
         </is>
       </c>
       <c r="F402" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="403">
@@ -11701,7 +11701,7 @@
         </is>
       </c>
       <c r="F403" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="404">
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="F404" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="405">
@@ -11757,7 +11757,7 @@
         </is>
       </c>
       <c r="F405" t="n">
-        <v>-1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="406">
@@ -11785,7 +11785,7 @@
         </is>
       </c>
       <c r="F406" t="n">
-        <v>-1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="407">
@@ -11813,7 +11813,7 @@
         </is>
       </c>
       <c r="F407" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="408">
@@ -11841,7 +11841,7 @@
         </is>
       </c>
       <c r="F408" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="409">
@@ -11897,7 +11897,7 @@
         </is>
       </c>
       <c r="F410" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="411">
@@ -11925,7 +11925,7 @@
         </is>
       </c>
       <c r="F411" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="412">
@@ -11953,7 +11953,7 @@
         </is>
       </c>
       <c r="F412" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="413">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="F415" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="416">
@@ -12065,7 +12065,7 @@
         </is>
       </c>
       <c r="F416" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="417">
@@ -12093,7 +12093,7 @@
         </is>
       </c>
       <c r="F417" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="418">
@@ -12149,7 +12149,7 @@
         </is>
       </c>
       <c r="F419" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="420">
@@ -12177,7 +12177,7 @@
         </is>
       </c>
       <c r="F420" t="n">
-        <v>-1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="421">
@@ -12205,7 +12205,7 @@
         </is>
       </c>
       <c r="F421" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="422">
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="F422" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="423">
@@ -12261,7 +12261,7 @@
         </is>
       </c>
       <c r="F423" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="424">
@@ -12289,7 +12289,7 @@
         </is>
       </c>
       <c r="F424" t="n">
-        <v>-1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="425">
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="F425" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="426">
@@ -12345,7 +12345,7 @@
         </is>
       </c>
       <c r="F426" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="427">
@@ -12401,7 +12401,7 @@
         </is>
       </c>
       <c r="F428" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="429">
@@ -12429,7 +12429,7 @@
         </is>
       </c>
       <c r="F429" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="430">
@@ -12457,7 +12457,7 @@
         </is>
       </c>
       <c r="F430" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="431">
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="F431" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="432">
@@ -12513,7 +12513,7 @@
         </is>
       </c>
       <c r="F432" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="433">
@@ -12541,7 +12541,7 @@
         </is>
       </c>
       <c r="F433" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="434">
@@ -12569,7 +12569,7 @@
         </is>
       </c>
       <c r="F434" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="435">
@@ -12597,7 +12597,7 @@
         </is>
       </c>
       <c r="F435" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="436">
@@ -12625,7 +12625,7 @@
         </is>
       </c>
       <c r="F436" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="437">
@@ -12653,7 +12653,7 @@
         </is>
       </c>
       <c r="F437" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="438">
@@ -12681,7 +12681,7 @@
         </is>
       </c>
       <c r="F438" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="439">
@@ -12709,7 +12709,7 @@
         </is>
       </c>
       <c r="F439" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="440">
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="F440" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="441">
@@ -12765,7 +12765,7 @@
         </is>
       </c>
       <c r="F441" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="442">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="F442" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="443">
@@ -12849,7 +12849,7 @@
         </is>
       </c>
       <c r="F444" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="445">
@@ -12877,7 +12877,7 @@
         </is>
       </c>
       <c r="F445" t="n">
-        <v>-1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="446">
@@ -12905,7 +12905,7 @@
         </is>
       </c>
       <c r="F446" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="447">
@@ -12933,7 +12933,7 @@
         </is>
       </c>
       <c r="F447" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="448">
@@ -12961,7 +12961,7 @@
         </is>
       </c>
       <c r="F448" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="449">
@@ -12989,7 +12989,7 @@
         </is>
       </c>
       <c r="F449" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="450">
@@ -13017,7 +13017,7 @@
         </is>
       </c>
       <c r="F450" t="n">
-        <v>-1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="451">
@@ -13045,7 +13045,7 @@
         </is>
       </c>
       <c r="F451" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -13073,7 +13073,7 @@
         </is>
       </c>
       <c r="F452" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="453">
@@ -13101,7 +13101,7 @@
         </is>
       </c>
       <c r="F453" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="454">
@@ -13129,7 +13129,7 @@
         </is>
       </c>
       <c r="F454" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="455">
@@ -13157,7 +13157,7 @@
         </is>
       </c>
       <c r="F455" t="n">
-        <v>-1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="456">
@@ -13213,7 +13213,7 @@
         </is>
       </c>
       <c r="F457" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="458">
@@ -13241,7 +13241,7 @@
         </is>
       </c>
       <c r="F458" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="459">
@@ -13269,7 +13269,7 @@
         </is>
       </c>
       <c r="F459" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="460">
@@ -13297,7 +13297,7 @@
         </is>
       </c>
       <c r="F460" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="461">
@@ -13381,7 +13381,7 @@
         </is>
       </c>
       <c r="F463" t="n">
-        <v>-1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="464">
@@ -13409,7 +13409,7 @@
         </is>
       </c>
       <c r="F464" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="465">
@@ -13437,7 +13437,7 @@
         </is>
       </c>
       <c r="F465" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="466">
@@ -13465,7 +13465,7 @@
         </is>
       </c>
       <c r="F466" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="467">
@@ -13493,7 +13493,7 @@
         </is>
       </c>
       <c r="F467" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="468">
@@ -13521,7 +13521,7 @@
         </is>
       </c>
       <c r="F468" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="469">
@@ -13549,7 +13549,7 @@
         </is>
       </c>
       <c r="F469" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="470">
@@ -13577,7 +13577,7 @@
         </is>
       </c>
       <c r="F470" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="471">
@@ -13605,7 +13605,7 @@
         </is>
       </c>
       <c r="F471" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="472">
@@ -13633,7 +13633,7 @@
         </is>
       </c>
       <c r="F472" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="473">
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="F473" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="474">
@@ -13689,7 +13689,7 @@
         </is>
       </c>
       <c r="F474" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="475">
@@ -13717,7 +13717,7 @@
         </is>
       </c>
       <c r="F475" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="476">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="F476" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="477">
@@ -13773,7 +13773,7 @@
         </is>
       </c>
       <c r="F477" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="478">
@@ -13801,7 +13801,7 @@
         </is>
       </c>
       <c r="F478" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="479">
@@ -13857,7 +13857,7 @@
         </is>
       </c>
       <c r="F480" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="481">
@@ -13885,7 +13885,7 @@
         </is>
       </c>
       <c r="F481" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="482">
@@ -13913,7 +13913,7 @@
         </is>
       </c>
       <c r="F482" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="483">
@@ -13941,7 +13941,7 @@
         </is>
       </c>
       <c r="F483" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="484">
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="F485" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="486">
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="F486" t="n">
-        <v>-1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="487">
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="F487" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="488">
@@ -14081,7 +14081,7 @@
         </is>
       </c>
       <c r="F488" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="489">
@@ -14109,7 +14109,7 @@
         </is>
       </c>
       <c r="F489" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="490">
@@ -14137,7 +14137,7 @@
         </is>
       </c>
       <c r="F490" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="491">
@@ -14193,7 +14193,7 @@
         </is>
       </c>
       <c r="F492" t="n">
-        <v>-1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="493">
@@ -14249,7 +14249,7 @@
         </is>
       </c>
       <c r="F494" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="495">
@@ -14277,7 +14277,7 @@
         </is>
       </c>
       <c r="F495" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="496">
@@ -14305,7 +14305,7 @@
         </is>
       </c>
       <c r="F496" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="497">
@@ -14333,7 +14333,7 @@
         </is>
       </c>
       <c r="F497" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="498">
@@ -14361,7 +14361,7 @@
         </is>
       </c>
       <c r="F498" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="499">
@@ -14389,7 +14389,7 @@
         </is>
       </c>
       <c r="F499" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="500">
@@ -14417,7 +14417,7 @@
         </is>
       </c>
       <c r="F500" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="501">
@@ -14445,7 +14445,7 @@
         </is>
       </c>
       <c r="F501" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="502">
@@ -14473,7 +14473,7 @@
         </is>
       </c>
       <c r="F502" t="n">
-        <v>-1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="503">
@@ -14501,7 +14501,7 @@
         </is>
       </c>
       <c r="F503" t="n">
-        <v>-1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="504">
@@ -14529,7 +14529,7 @@
         </is>
       </c>
       <c r="F504" t="n">
-        <v>-1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="505">
@@ -14557,7 +14557,7 @@
         </is>
       </c>
       <c r="F505" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="506">
@@ -14585,7 +14585,7 @@
         </is>
       </c>
       <c r="F506" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="507">
@@ -14613,7 +14613,7 @@
         </is>
       </c>
       <c r="F507" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="508">
@@ -14641,7 +14641,7 @@
         </is>
       </c>
       <c r="F508" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="509">
@@ -14669,7 +14669,7 @@
         </is>
       </c>
       <c r="F509" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="510">
@@ -14697,7 +14697,7 @@
         </is>
       </c>
       <c r="F510" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="511">
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="F512" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="513">
@@ -14781,7 +14781,7 @@
         </is>
       </c>
       <c r="F513" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
     </row>
     <row r="514">
@@ -14809,7 +14809,7 @@
         </is>
       </c>
       <c r="F514" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="515">
@@ -14837,7 +14837,7 @@
         </is>
       </c>
       <c r="F515" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="516">
@@ -14865,7 +14865,7 @@
         </is>
       </c>
       <c r="F516" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="517">
@@ -14893,7 +14893,7 @@
         </is>
       </c>
       <c r="F517" t="n">
-        <v>-1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="518">
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="F518" t="n">
-        <v>-1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="519">
@@ -14949,7 +14949,7 @@
         </is>
       </c>
       <c r="F519" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="520">
@@ -14977,7 +14977,7 @@
         </is>
       </c>
       <c r="F520" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="521">
@@ -15005,7 +15005,7 @@
         </is>
       </c>
       <c r="F521" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="522">
@@ -15033,7 +15033,7 @@
         </is>
       </c>
       <c r="F522" t="n">
-        <v>-1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="523">
@@ -15061,7 +15061,7 @@
         </is>
       </c>
       <c r="F523" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="524">
@@ -15089,7 +15089,7 @@
         </is>
       </c>
       <c r="F524" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="525">
@@ -15117,7 +15117,7 @@
         </is>
       </c>
       <c r="F525" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
     </row>
     <row r="526">
@@ -15145,7 +15145,7 @@
         </is>
       </c>
       <c r="F526" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="527">
@@ -15201,7 +15201,7 @@
         </is>
       </c>
       <c r="F528" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="529">
@@ -15257,7 +15257,7 @@
         </is>
       </c>
       <c r="F530" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="531">
@@ -15285,7 +15285,7 @@
         </is>
       </c>
       <c r="F531" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="532">
@@ -15313,7 +15313,7 @@
         </is>
       </c>
       <c r="F532" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="533">
@@ -15341,7 +15341,7 @@
         </is>
       </c>
       <c r="F533" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="534">
@@ -15369,7 +15369,7 @@
         </is>
       </c>
       <c r="F534" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="535">
@@ -15397,7 +15397,7 @@
         </is>
       </c>
       <c r="F535" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="536">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="F537" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="538">
@@ -15509,7 +15509,7 @@
         </is>
       </c>
       <c r="F539" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="540">
@@ -15537,7 +15537,7 @@
         </is>
       </c>
       <c r="F540" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="541">
@@ -15565,7 +15565,7 @@
         </is>
       </c>
       <c r="F541" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="542">
@@ -15621,7 +15621,7 @@
         </is>
       </c>
       <c r="F543" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="544">
@@ -15649,7 +15649,7 @@
         </is>
       </c>
       <c r="F544" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="545">
@@ -15677,7 +15677,7 @@
         </is>
       </c>
       <c r="F545" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="546">
@@ -15705,7 +15705,7 @@
         </is>
       </c>
       <c r="F546" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="547">
@@ -15733,7 +15733,7 @@
         </is>
       </c>
       <c r="F547" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="548">
@@ -15761,7 +15761,7 @@
         </is>
       </c>
       <c r="F548" t="n">
-        <v>-1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="549">
@@ -15789,7 +15789,7 @@
         </is>
       </c>
       <c r="F549" t="n">
-        <v>-1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="550">
@@ -15873,7 +15873,7 @@
         </is>
       </c>
       <c r="F552" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="553">
@@ -15901,7 +15901,7 @@
         </is>
       </c>
       <c r="F553" t="n">
-        <v>-1</v>
+        <v>41</v>
       </c>
     </row>
     <row r="554">
@@ -15929,7 +15929,7 @@
         </is>
       </c>
       <c r="F554" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="555">
@@ -15957,7 +15957,7 @@
         </is>
       </c>
       <c r="F555" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="556">
@@ -15985,7 +15985,7 @@
         </is>
       </c>
       <c r="F556" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="557">
@@ -16013,7 +16013,7 @@
         </is>
       </c>
       <c r="F557" t="n">
-        <v>-1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="558">
@@ -16041,7 +16041,7 @@
         </is>
       </c>
       <c r="F558" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="559">
@@ -16097,7 +16097,7 @@
         </is>
       </c>
       <c r="F560" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="561">
@@ -16125,7 +16125,7 @@
         </is>
       </c>
       <c r="F561" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="562">
@@ -16181,7 +16181,7 @@
         </is>
       </c>
       <c r="F563" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="564">
@@ -16237,7 +16237,7 @@
         </is>
       </c>
       <c r="F565" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="566">
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="F566" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="567">
@@ -16293,7 +16293,7 @@
         </is>
       </c>
       <c r="F567" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="568">
@@ -16321,7 +16321,7 @@
         </is>
       </c>
       <c r="F568" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="569">
@@ -16349,7 +16349,7 @@
         </is>
       </c>
       <c r="F569" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="570">
@@ -16377,7 +16377,7 @@
         </is>
       </c>
       <c r="F570" t="n">
-        <v>34</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="571">
@@ -16405,7 +16405,7 @@
         </is>
       </c>
       <c r="F571" t="n">
-        <v>-1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="572">
@@ -16433,7 +16433,7 @@
         </is>
       </c>
       <c r="F572" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="573">
@@ -16461,7 +16461,7 @@
         </is>
       </c>
       <c r="F573" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="574">
@@ -16489,7 +16489,7 @@
         </is>
       </c>
       <c r="F574" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="575">
@@ -16517,7 +16517,7 @@
         </is>
       </c>
       <c r="F575" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="576">
@@ -16545,7 +16545,7 @@
         </is>
       </c>
       <c r="F576" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="577">
@@ -16573,7 +16573,7 @@
         </is>
       </c>
       <c r="F577" t="n">
-        <v>-1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="578">
@@ -16601,7 +16601,7 @@
         </is>
       </c>
       <c r="F578" t="n">
-        <v>-1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="579">
@@ -16657,7 +16657,7 @@
         </is>
       </c>
       <c r="F580" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="581">
@@ -16685,7 +16685,7 @@
         </is>
       </c>
       <c r="F581" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="582">
@@ -16713,7 +16713,7 @@
         </is>
       </c>
       <c r="F582" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="583">
@@ -16741,7 +16741,7 @@
         </is>
       </c>
       <c r="F583" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="584">
@@ -16769,7 +16769,7 @@
         </is>
       </c>
       <c r="F584" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="585">
@@ -16853,7 +16853,7 @@
         </is>
       </c>
       <c r="F587" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="588">
@@ -16909,7 +16909,7 @@
         </is>
       </c>
       <c r="F589" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="590">
@@ -16937,7 +16937,7 @@
         </is>
       </c>
       <c r="F590" t="n">
-        <v>-1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="591">
@@ -16993,7 +16993,7 @@
         </is>
       </c>
       <c r="F592" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="593">
@@ -17021,7 +17021,7 @@
         </is>
       </c>
       <c r="F593" t="n">
-        <v>-1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="594">
@@ -17077,7 +17077,7 @@
         </is>
       </c>
       <c r="F595" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="596">
@@ -17105,7 +17105,7 @@
         </is>
       </c>
       <c r="F596" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="597">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="F598" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="599">
@@ -17189,7 +17189,7 @@
         </is>
       </c>
       <c r="F599" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="600">
@@ -17217,7 +17217,7 @@
         </is>
       </c>
       <c r="F600" t="n">
-        <v>-1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="601">
@@ -17245,7 +17245,7 @@
         </is>
       </c>
       <c r="F601" t="n">
-        <v>-1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="602">
@@ -17301,7 +17301,7 @@
         </is>
       </c>
       <c r="F603" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="604">
@@ -17329,7 +17329,7 @@
         </is>
       </c>
       <c r="F604" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="605">
@@ -17357,7 +17357,7 @@
         </is>
       </c>
       <c r="F605" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="606">
@@ -17385,7 +17385,7 @@
         </is>
       </c>
       <c r="F606" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="607">
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="F607" t="n">
-        <v>-1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="608">
@@ -17469,7 +17469,7 @@
         </is>
       </c>
       <c r="F609" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="610">
@@ -17525,7 +17525,7 @@
         </is>
       </c>
       <c r="F611" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="612">
@@ -17553,7 +17553,7 @@
         </is>
       </c>
       <c r="F612" t="n">
-        <v>-1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="613">
@@ -17581,7 +17581,7 @@
         </is>
       </c>
       <c r="F613" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="614">
@@ -17609,7 +17609,7 @@
         </is>
       </c>
       <c r="F614" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="615">
@@ -17665,7 +17665,7 @@
         </is>
       </c>
       <c r="F616" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="617">
@@ -17693,7 +17693,7 @@
         </is>
       </c>
       <c r="F617" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="618">
@@ -17721,7 +17721,7 @@
         </is>
       </c>
       <c r="F618" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="619">
@@ -17749,7 +17749,7 @@
         </is>
       </c>
       <c r="F619" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="620">
@@ -17777,7 +17777,7 @@
         </is>
       </c>
       <c r="F620" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="621">
@@ -17805,7 +17805,7 @@
         </is>
       </c>
       <c r="F621" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="622">
@@ -17833,7 +17833,7 @@
         </is>
       </c>
       <c r="F622" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="623">
@@ -17861,7 +17861,7 @@
         </is>
       </c>
       <c r="F623" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="624">
@@ -17917,7 +17917,7 @@
         </is>
       </c>
       <c r="F625" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="626">
@@ -17945,7 +17945,7 @@
         </is>
       </c>
       <c r="F626" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="627">
@@ -17973,7 +17973,7 @@
         </is>
       </c>
       <c r="F627" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="628">
@@ -18001,7 +18001,7 @@
         </is>
       </c>
       <c r="F628" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="629">
@@ -18057,7 +18057,7 @@
         </is>
       </c>
       <c r="F630" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="631">
@@ -18113,7 +18113,7 @@
         </is>
       </c>
       <c r="F632" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="633">
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="F633" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="634">
@@ -18169,7 +18169,7 @@
         </is>
       </c>
       <c r="F634" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
     </row>
     <row r="635">
@@ -18225,7 +18225,7 @@
         </is>
       </c>
       <c r="F636" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="637">
@@ -18337,7 +18337,7 @@
         </is>
       </c>
       <c r="F640" t="n">
-        <v>-1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="641">
@@ -18393,7 +18393,7 @@
         </is>
       </c>
       <c r="F642" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="643">
@@ -18421,7 +18421,7 @@
         </is>
       </c>
       <c r="F643" t="n">
-        <v>-1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="644">
@@ -18449,7 +18449,7 @@
         </is>
       </c>
       <c r="F644" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="645">
@@ -18477,7 +18477,7 @@
         </is>
       </c>
       <c r="F645" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="646">
@@ -18505,7 +18505,7 @@
         </is>
       </c>
       <c r="F646" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="647">
@@ -18533,7 +18533,7 @@
         </is>
       </c>
       <c r="F647" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="648">
@@ -18561,7 +18561,7 @@
         </is>
       </c>
       <c r="F648" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="649">
@@ -18589,7 +18589,7 @@
         </is>
       </c>
       <c r="F649" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="650">
@@ -18617,7 +18617,7 @@
         </is>
       </c>
       <c r="F650" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="651">
@@ -18645,7 +18645,7 @@
         </is>
       </c>
       <c r="F651" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="652">
@@ -18673,7 +18673,7 @@
         </is>
       </c>
       <c r="F652" t="n">
-        <v>-1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="653">
@@ -18701,7 +18701,7 @@
         </is>
       </c>
       <c r="F653" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="654">
@@ -18729,7 +18729,7 @@
         </is>
       </c>
       <c r="F654" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="655">
@@ -18757,7 +18757,7 @@
         </is>
       </c>
       <c r="F655" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="656">
@@ -18785,7 +18785,7 @@
         </is>
       </c>
       <c r="F656" t="n">
-        <v>-1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="657">
@@ -18841,7 +18841,7 @@
         </is>
       </c>
       <c r="F658" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="659">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="F659" t="n">
-        <v>-1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="660">
@@ -18897,7 +18897,7 @@
         </is>
       </c>
       <c r="F660" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="661">
@@ -18925,7 +18925,7 @@
         </is>
       </c>
       <c r="F661" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="662">
@@ -18953,7 +18953,7 @@
         </is>
       </c>
       <c r="F662" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="663">
@@ -19009,7 +19009,7 @@
         </is>
       </c>
       <c r="F664" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="665">
@@ -19037,7 +19037,7 @@
         </is>
       </c>
       <c r="F665" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="666">
@@ -19065,7 +19065,7 @@
         </is>
       </c>
       <c r="F666" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="667">
@@ -19093,7 +19093,7 @@
         </is>
       </c>
       <c r="F667" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="668">
@@ -19121,7 +19121,7 @@
         </is>
       </c>
       <c r="F668" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="669">
@@ -19149,7 +19149,7 @@
         </is>
       </c>
       <c r="F669" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="670">
@@ -19177,7 +19177,7 @@
         </is>
       </c>
       <c r="F670" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
     </row>
     <row r="671">
@@ -19233,7 +19233,7 @@
         </is>
       </c>
       <c r="F672" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="673">
@@ -19261,7 +19261,7 @@
         </is>
       </c>
       <c r="F673" t="n">
-        <v>-1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="674">
@@ -19289,7 +19289,7 @@
         </is>
       </c>
       <c r="F674" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="675">
@@ -19317,7 +19317,7 @@
         </is>
       </c>
       <c r="F675" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="676">
@@ -19373,7 +19373,7 @@
         </is>
       </c>
       <c r="F677" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="678">
@@ -19401,7 +19401,7 @@
         </is>
       </c>
       <c r="F678" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="679">
@@ -19429,7 +19429,7 @@
         </is>
       </c>
       <c r="F679" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="680">
@@ -19457,7 +19457,7 @@
         </is>
       </c>
       <c r="F680" t="n">
-        <v>-1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="681">
@@ -19513,7 +19513,7 @@
         </is>
       </c>
       <c r="F682" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="683">
@@ -19541,7 +19541,7 @@
         </is>
       </c>
       <c r="F683" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="684">
@@ -19569,7 +19569,7 @@
         </is>
       </c>
       <c r="F684" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="685">
@@ -19597,7 +19597,7 @@
         </is>
       </c>
       <c r="F685" t="n">
-        <v>-1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="686">
@@ -19653,7 +19653,7 @@
         </is>
       </c>
       <c r="F687" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="688">
@@ -19681,7 +19681,7 @@
         </is>
       </c>
       <c r="F688" t="n">
-        <v>-1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="689">
@@ -19709,7 +19709,7 @@
         </is>
       </c>
       <c r="F689" t="n">
-        <v>-1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="690">
@@ -19793,7 +19793,7 @@
         </is>
       </c>
       <c r="F692" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="693">
@@ -19821,7 +19821,7 @@
         </is>
       </c>
       <c r="F693" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="694">
@@ -19849,7 +19849,7 @@
         </is>
       </c>
       <c r="F694" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="695">
@@ -19877,7 +19877,7 @@
         </is>
       </c>
       <c r="F695" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="696">
@@ -19905,7 +19905,7 @@
         </is>
       </c>
       <c r="F696" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="697">
@@ -19933,7 +19933,7 @@
         </is>
       </c>
       <c r="F697" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="698">
@@ -19989,7 +19989,7 @@
         </is>
       </c>
       <c r="F699" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="700">
@@ -20017,7 +20017,7 @@
         </is>
       </c>
       <c r="F700" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="701">
@@ -20073,7 +20073,7 @@
         </is>
       </c>
       <c r="F702" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="703">
@@ -20101,7 +20101,7 @@
         </is>
       </c>
       <c r="F703" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="704">
@@ -20129,7 +20129,7 @@
         </is>
       </c>
       <c r="F704" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="705">
@@ -20157,7 +20157,7 @@
         </is>
       </c>
       <c r="F705" t="n">
-        <v>-1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="706">
@@ -20185,7 +20185,7 @@
         </is>
       </c>
       <c r="F706" t="n">
-        <v>-1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="707">
@@ -20213,7 +20213,7 @@
         </is>
       </c>
       <c r="F707" t="n">
-        <v>19</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="708">
@@ -20241,7 +20241,7 @@
         </is>
       </c>
       <c r="F708" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="709">
@@ -20269,7 +20269,7 @@
         </is>
       </c>
       <c r="F709" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="710">
@@ -20297,7 +20297,7 @@
         </is>
       </c>
       <c r="F710" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="711">
@@ -20325,7 +20325,7 @@
         </is>
       </c>
       <c r="F711" t="n">
-        <v>-1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="712">
@@ -20353,7 +20353,7 @@
         </is>
       </c>
       <c r="F712" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="713">
@@ -20381,7 +20381,7 @@
         </is>
       </c>
       <c r="F713" t="n">
-        <v>-1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="714">
@@ -20437,7 +20437,7 @@
         </is>
       </c>
       <c r="F715" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="716">
@@ -20465,7 +20465,7 @@
         </is>
       </c>
       <c r="F716" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="717">
@@ -20493,7 +20493,7 @@
         </is>
       </c>
       <c r="F717" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="718">
@@ -20521,7 +20521,7 @@
         </is>
       </c>
       <c r="F718" t="n">
-        <v>-1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="719">
@@ -20549,7 +20549,7 @@
         </is>
       </c>
       <c r="F719" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="720">
@@ -20605,7 +20605,7 @@
         </is>
       </c>
       <c r="F721" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="722">
@@ -20633,7 +20633,7 @@
         </is>
       </c>
       <c r="F722" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="723">
@@ -20689,7 +20689,7 @@
         </is>
       </c>
       <c r="F724" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="725">
@@ -20717,7 +20717,7 @@
         </is>
       </c>
       <c r="F725" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="726">
@@ -20745,7 +20745,7 @@
         </is>
       </c>
       <c r="F726" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="727">
@@ -20829,7 +20829,7 @@
         </is>
       </c>
       <c r="F729" t="n">
-        <v>-1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="730">
@@ -20885,7 +20885,7 @@
         </is>
       </c>
       <c r="F731" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="732">
@@ -20913,7 +20913,7 @@
         </is>
       </c>
       <c r="F732" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="733">
@@ -20969,7 +20969,7 @@
         </is>
       </c>
       <c r="F734" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="735">
@@ -20997,7 +20997,7 @@
         </is>
       </c>
       <c r="F735" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="736">
@@ -21025,7 +21025,7 @@
         </is>
       </c>
       <c r="F736" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="737">
@@ -21081,7 +21081,7 @@
         </is>
       </c>
       <c r="F738" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="739">
@@ -21109,7 +21109,7 @@
         </is>
       </c>
       <c r="F739" t="n">
-        <v>-1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="740">
@@ -21137,7 +21137,7 @@
         </is>
       </c>
       <c r="F740" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="741">
@@ -21165,7 +21165,7 @@
         </is>
       </c>
       <c r="F741" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="742">
@@ -21193,7 +21193,7 @@
         </is>
       </c>
       <c r="F742" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="743">
@@ -21221,7 +21221,7 @@
         </is>
       </c>
       <c r="F743" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="744">
@@ -21249,7 +21249,7 @@
         </is>
       </c>
       <c r="F744" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="745">
@@ -21277,7 +21277,7 @@
         </is>
       </c>
       <c r="F745" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="746">
@@ -21305,7 +21305,7 @@
         </is>
       </c>
       <c r="F746" t="n">
-        <v>-1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="747">
@@ -21333,7 +21333,7 @@
         </is>
       </c>
       <c r="F747" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="748">
@@ -21361,7 +21361,7 @@
         </is>
       </c>
       <c r="F748" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="749">
@@ -21389,7 +21389,7 @@
         </is>
       </c>
       <c r="F749" t="n">
-        <v>-1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="750">
@@ -21417,7 +21417,7 @@
         </is>
       </c>
       <c r="F750" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="751">
@@ -21445,7 +21445,7 @@
         </is>
       </c>
       <c r="F751" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="752">
@@ -21473,7 +21473,7 @@
         </is>
       </c>
       <c r="F752" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="753">
@@ -21529,7 +21529,7 @@
         </is>
       </c>
       <c r="F754" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="755">
@@ -21557,7 +21557,7 @@
         </is>
       </c>
       <c r="F755" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="756">
@@ -21585,7 +21585,7 @@
         </is>
       </c>
       <c r="F756" t="n">
-        <v>-1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="757">
@@ -21613,7 +21613,7 @@
         </is>
       </c>
       <c r="F757" t="n">
-        <v>-1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="758">
@@ -21641,7 +21641,7 @@
         </is>
       </c>
       <c r="F758" t="n">
-        <v>-1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="759">
@@ -21669,7 +21669,7 @@
         </is>
       </c>
       <c r="F759" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="760">
@@ -21697,7 +21697,7 @@
         </is>
       </c>
       <c r="F760" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="761">
@@ -21725,7 +21725,7 @@
         </is>
       </c>
       <c r="F761" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="762">
@@ -21753,7 +21753,7 @@
         </is>
       </c>
       <c r="F762" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="763">
@@ -21781,7 +21781,7 @@
         </is>
       </c>
       <c r="F763" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="764">
@@ -21809,7 +21809,7 @@
         </is>
       </c>
       <c r="F764" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="765">
@@ -21893,7 +21893,7 @@
         </is>
       </c>
       <c r="F767" t="n">
-        <v>-1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="768">
@@ -21921,7 +21921,7 @@
         </is>
       </c>
       <c r="F768" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="769">
@@ -21949,7 +21949,7 @@
         </is>
       </c>
       <c r="F769" t="n">
-        <v>-1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="770">
@@ -21977,7 +21977,7 @@
         </is>
       </c>
       <c r="F770" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="771">
@@ -22005,7 +22005,7 @@
         </is>
       </c>
       <c r="F771" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="772">
@@ -22089,7 +22089,7 @@
         </is>
       </c>
       <c r="F774" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="775">
@@ -22117,7 +22117,7 @@
         </is>
       </c>
       <c r="F775" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="776">
@@ -22201,7 +22201,7 @@
         </is>
       </c>
       <c r="F778" t="n">
-        <v>-1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="779">
@@ -22229,7 +22229,7 @@
         </is>
       </c>
       <c r="F779" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="780">
@@ -22257,7 +22257,7 @@
         </is>
       </c>
       <c r="F780" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="781">
@@ -22285,7 +22285,7 @@
         </is>
       </c>
       <c r="F781" t="n">
-        <v>31</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="782">
@@ -22313,7 +22313,7 @@
         </is>
       </c>
       <c r="F782" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="783">
@@ -22341,7 +22341,7 @@
         </is>
       </c>
       <c r="F783" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="784">
@@ -22425,7 +22425,7 @@
         </is>
       </c>
       <c r="F786" t="n">
-        <v>-1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="787">
@@ -22453,7 +22453,7 @@
         </is>
       </c>
       <c r="F787" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="788">
@@ -22537,7 +22537,7 @@
         </is>
       </c>
       <c r="F790" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="791">
@@ -22565,7 +22565,7 @@
         </is>
       </c>
       <c r="F791" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="792">
@@ -22593,7 +22593,7 @@
         </is>
       </c>
       <c r="F792" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="793">
@@ -22621,7 +22621,7 @@
         </is>
       </c>
       <c r="F793" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="794">
@@ -22649,7 +22649,7 @@
         </is>
       </c>
       <c r="F794" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="795">
@@ -22705,7 +22705,7 @@
         </is>
       </c>
       <c r="F796" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="797">
@@ -22733,7 +22733,7 @@
         </is>
       </c>
       <c r="F797" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="798">
@@ -22761,7 +22761,7 @@
         </is>
       </c>
       <c r="F798" t="n">
-        <v>-1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="799">
@@ -22817,7 +22817,7 @@
         </is>
       </c>
       <c r="F800" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="801">
@@ -22845,7 +22845,7 @@
         </is>
       </c>
       <c r="F801" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="802">
@@ -22873,7 +22873,7 @@
         </is>
       </c>
       <c r="F802" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="803">
@@ -22901,7 +22901,7 @@
         </is>
       </c>
       <c r="F803" t="n">
-        <v>-1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="804">
@@ -22929,7 +22929,7 @@
         </is>
       </c>
       <c r="F804" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="805">
@@ -22957,7 +22957,7 @@
         </is>
       </c>
       <c r="F805" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="806">
@@ -22985,7 +22985,7 @@
         </is>
       </c>
       <c r="F806" t="n">
-        <v>-1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="807">
@@ -23013,7 +23013,7 @@
         </is>
       </c>
       <c r="F807" t="n">
-        <v>-1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="808">
@@ -23041,7 +23041,7 @@
         </is>
       </c>
       <c r="F808" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="809">
@@ -23069,7 +23069,7 @@
         </is>
       </c>
       <c r="F809" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="810">
@@ -23097,7 +23097,7 @@
         </is>
       </c>
       <c r="F810" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="811">
@@ -23125,7 +23125,7 @@
         </is>
       </c>
       <c r="F811" t="n">
-        <v>-1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="812">
@@ -23153,7 +23153,7 @@
         </is>
       </c>
       <c r="F812" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="813">
@@ -23181,7 +23181,7 @@
         </is>
       </c>
       <c r="F813" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="814">
@@ -23209,7 +23209,7 @@
         </is>
       </c>
       <c r="F814" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="815">
@@ -23237,7 +23237,7 @@
         </is>
       </c>
       <c r="F815" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="816">
@@ -23293,7 +23293,7 @@
         </is>
       </c>
       <c r="F817" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="818">
@@ -23321,7 +23321,7 @@
         </is>
       </c>
       <c r="F818" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="819">
@@ -23349,7 +23349,7 @@
         </is>
       </c>
       <c r="F819" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="820">
@@ -23405,7 +23405,7 @@
         </is>
       </c>
       <c r="F821" t="n">
-        <v>-1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="822">
@@ -23461,7 +23461,7 @@
         </is>
       </c>
       <c r="F823" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="824">
@@ -23489,7 +23489,7 @@
         </is>
       </c>
       <c r="F824" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="825">
@@ -23545,7 +23545,7 @@
         </is>
       </c>
       <c r="F826" t="n">
-        <v>-1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="827">
@@ -23573,7 +23573,7 @@
         </is>
       </c>
       <c r="F827" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="828">
@@ -23601,7 +23601,7 @@
         </is>
       </c>
       <c r="F828" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="829">
@@ -23629,7 +23629,7 @@
         </is>
       </c>
       <c r="F829" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="830">
@@ -23657,7 +23657,7 @@
         </is>
       </c>
       <c r="F830" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="831">
@@ -23685,7 +23685,7 @@
         </is>
       </c>
       <c r="F831" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="832">
@@ -23713,7 +23713,7 @@
         </is>
       </c>
       <c r="F832" t="n">
-        <v>-1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="833">
@@ -23741,7 +23741,7 @@
         </is>
       </c>
       <c r="F833" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="834">
@@ -23769,7 +23769,7 @@
         </is>
       </c>
       <c r="F834" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="835">
@@ -23797,7 +23797,7 @@
         </is>
       </c>
       <c r="F835" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="836">
@@ -23825,7 +23825,7 @@
         </is>
       </c>
       <c r="F836" t="n">
-        <v>-1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="837">
@@ -23853,7 +23853,7 @@
         </is>
       </c>
       <c r="F837" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="838">
@@ -23881,7 +23881,7 @@
         </is>
       </c>
       <c r="F838" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
     </row>
     <row r="839">
@@ -23965,7 +23965,7 @@
         </is>
       </c>
       <c r="F841" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="842">
@@ -23993,7 +23993,7 @@
         </is>
       </c>
       <c r="F842" t="n">
-        <v>-1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="843">
@@ -24021,7 +24021,7 @@
         </is>
       </c>
       <c r="F843" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="844">
@@ -24049,7 +24049,7 @@
         </is>
       </c>
       <c r="F844" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="845">
@@ -24077,7 +24077,7 @@
         </is>
       </c>
       <c r="F845" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="846">
@@ -24105,7 +24105,7 @@
         </is>
       </c>
       <c r="F846" t="n">
-        <v>-1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="847">
@@ -24133,7 +24133,7 @@
         </is>
       </c>
       <c r="F847" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="848">
@@ -24189,7 +24189,7 @@
         </is>
       </c>
       <c r="F849" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="850">
@@ -24217,7 +24217,7 @@
         </is>
       </c>
       <c r="F850" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="851">
@@ -24273,7 +24273,7 @@
         </is>
       </c>
       <c r="F852" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="853">
@@ -24329,7 +24329,7 @@
         </is>
       </c>
       <c r="F854" t="n">
-        <v>-1</v>
+        <v>41</v>
       </c>
     </row>
     <row r="855">
@@ -24357,7 +24357,7 @@
         </is>
       </c>
       <c r="F855" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="856">
@@ -24385,7 +24385,7 @@
         </is>
       </c>
       <c r="F856" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
     </row>
     <row r="857">
@@ -24413,7 +24413,7 @@
         </is>
       </c>
       <c r="F857" t="n">
-        <v>-1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="858">
@@ -24441,7 +24441,7 @@
         </is>
       </c>
       <c r="F858" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="859">
@@ -24469,7 +24469,7 @@
         </is>
       </c>
       <c r="F859" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="860">
@@ -24497,7 +24497,7 @@
         </is>
       </c>
       <c r="F860" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="861">
@@ -24525,7 +24525,7 @@
         </is>
       </c>
       <c r="F861" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="862">
@@ -24553,7 +24553,7 @@
         </is>
       </c>
       <c r="F862" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="863">
@@ -24581,7 +24581,7 @@
         </is>
       </c>
       <c r="F863" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="864">
@@ -24609,7 +24609,7 @@
         </is>
       </c>
       <c r="F864" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="865">
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="F865" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="866">
@@ -24665,7 +24665,7 @@
         </is>
       </c>
       <c r="F866" t="n">
-        <v>-1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="867">
@@ -24693,7 +24693,7 @@
         </is>
       </c>
       <c r="F867" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="868">
@@ -24721,7 +24721,7 @@
         </is>
       </c>
       <c r="F868" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="869">
@@ -24749,7 +24749,7 @@
         </is>
       </c>
       <c r="F869" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="870">
@@ -24777,7 +24777,7 @@
         </is>
       </c>
       <c r="F870" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="871">
@@ -24805,7 +24805,7 @@
         </is>
       </c>
       <c r="F871" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="872">
@@ -24861,7 +24861,7 @@
         </is>
       </c>
       <c r="F873" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="874">
@@ -24889,7 +24889,7 @@
         </is>
       </c>
       <c r="F874" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="875">
@@ -24917,7 +24917,7 @@
         </is>
       </c>
       <c r="F875" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="876">
@@ -24945,7 +24945,7 @@
         </is>
       </c>
       <c r="F876" t="n">
-        <v>-1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="877">
@@ -25057,7 +25057,7 @@
         </is>
       </c>
       <c r="F880" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="881">
@@ -25085,7 +25085,7 @@
         </is>
       </c>
       <c r="F881" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="882">
@@ -25113,7 +25113,7 @@
         </is>
       </c>
       <c r="F882" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="883">
@@ -25141,7 +25141,7 @@
         </is>
       </c>
       <c r="F883" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="884">
@@ -25169,7 +25169,7 @@
         </is>
       </c>
       <c r="F884" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="885">
@@ -25197,7 +25197,7 @@
         </is>
       </c>
       <c r="F885" t="n">
-        <v>-1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="886">
@@ -25225,7 +25225,7 @@
         </is>
       </c>
       <c r="F886" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="887">
@@ -25253,7 +25253,7 @@
         </is>
       </c>
       <c r="F887" t="n">
-        <v>-1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="888">
@@ -25281,7 +25281,7 @@
         </is>
       </c>
       <c r="F888" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="889">
@@ -25309,7 +25309,7 @@
         </is>
       </c>
       <c r="F889" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="890">
@@ -25337,7 +25337,7 @@
         </is>
       </c>
       <c r="F890" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="891">
@@ -25365,7 +25365,7 @@
         </is>
       </c>
       <c r="F891" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="892">
@@ -25393,7 +25393,7 @@
         </is>
       </c>
       <c r="F892" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="893">
@@ -25421,7 +25421,7 @@
         </is>
       </c>
       <c r="F893" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="894">
@@ -25449,7 +25449,7 @@
         </is>
       </c>
       <c r="F894" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="895">
@@ -25477,7 +25477,7 @@
         </is>
       </c>
       <c r="F895" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="896">
@@ -25505,7 +25505,7 @@
         </is>
       </c>
       <c r="F896" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="897">
@@ -25533,7 +25533,7 @@
         </is>
       </c>
       <c r="F897" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="898">
@@ -25561,7 +25561,7 @@
         </is>
       </c>
       <c r="F898" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="899">
@@ -25589,7 +25589,7 @@
         </is>
       </c>
       <c r="F899" t="n">
-        <v>-1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="900">
@@ -25645,7 +25645,7 @@
         </is>
       </c>
       <c r="F901" t="n">
-        <v>-1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="902">
@@ -25701,7 +25701,7 @@
         </is>
       </c>
       <c r="F903" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="904">
@@ -25729,7 +25729,7 @@
         </is>
       </c>
       <c r="F904" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="905">
@@ -25757,7 +25757,7 @@
         </is>
       </c>
       <c r="F905" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="906">
@@ -25785,7 +25785,7 @@
         </is>
       </c>
       <c r="F906" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="907">
@@ -25841,7 +25841,7 @@
         </is>
       </c>
       <c r="F908" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="909">
@@ -25869,7 +25869,7 @@
         </is>
       </c>
       <c r="F909" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="910">
@@ -25897,7 +25897,7 @@
         </is>
       </c>
       <c r="F910" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
     </row>
     <row r="911">
@@ -25953,7 +25953,7 @@
         </is>
       </c>
       <c r="F912" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="913">
@@ -25981,7 +25981,7 @@
         </is>
       </c>
       <c r="F913" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="914">
@@ -26009,7 +26009,7 @@
         </is>
       </c>
       <c r="F914" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="915">
@@ -26037,7 +26037,7 @@
         </is>
       </c>
       <c r="F915" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="916">
@@ -26065,7 +26065,7 @@
         </is>
       </c>
       <c r="F916" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="917">
@@ -26093,7 +26093,7 @@
         </is>
       </c>
       <c r="F917" t="n">
-        <v>-1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="918">
@@ -26121,7 +26121,7 @@
         </is>
       </c>
       <c r="F918" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="919">
@@ -26149,7 +26149,7 @@
         </is>
       </c>
       <c r="F919" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="920">
@@ -26177,7 +26177,7 @@
         </is>
       </c>
       <c r="F920" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="921">
@@ -26205,7 +26205,7 @@
         </is>
       </c>
       <c r="F921" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="922">
@@ -26317,7 +26317,7 @@
         </is>
       </c>
       <c r="F925" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="926">
@@ -26345,7 +26345,7 @@
         </is>
       </c>
       <c r="F926" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="927">
@@ -26373,7 +26373,7 @@
         </is>
       </c>
       <c r="F927" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="928">
@@ -26401,7 +26401,7 @@
         </is>
       </c>
       <c r="F928" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="929">
@@ -26429,7 +26429,7 @@
         </is>
       </c>
       <c r="F929" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="930">
@@ -26457,7 +26457,7 @@
         </is>
       </c>
       <c r="F930" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="931">
@@ -26513,7 +26513,7 @@
         </is>
       </c>
       <c r="F932" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="933">
@@ -26541,7 +26541,7 @@
         </is>
       </c>
       <c r="F933" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="934">
@@ -26597,7 +26597,7 @@
         </is>
       </c>
       <c r="F935" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="936">
@@ -26625,7 +26625,7 @@
         </is>
       </c>
       <c r="F936" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="937">
@@ -26653,7 +26653,7 @@
         </is>
       </c>
       <c r="F937" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="938">
@@ -26737,7 +26737,7 @@
         </is>
       </c>
       <c r="F940" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="941">
@@ -26765,7 +26765,7 @@
         </is>
       </c>
       <c r="F941" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="942">
@@ -26793,7 +26793,7 @@
         </is>
       </c>
       <c r="F942" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="943">
@@ -26821,7 +26821,7 @@
         </is>
       </c>
       <c r="F943" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="944">
@@ -26877,7 +26877,7 @@
         </is>
       </c>
       <c r="F945" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="946">
@@ -26905,7 +26905,7 @@
         </is>
       </c>
       <c r="F946" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="947">
@@ -26933,7 +26933,7 @@
         </is>
       </c>
       <c r="F947" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="948">
@@ -26961,7 +26961,7 @@
         </is>
       </c>
       <c r="F948" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="949">
@@ -27045,7 +27045,7 @@
         </is>
       </c>
       <c r="F951" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="952">
@@ -27129,7 +27129,7 @@
         </is>
       </c>
       <c r="F954" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="955">
@@ -27157,7 +27157,7 @@
         </is>
       </c>
       <c r="F955" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="956">
@@ -27213,7 +27213,7 @@
         </is>
       </c>
       <c r="F957" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="958">
@@ -27241,7 +27241,7 @@
         </is>
       </c>
       <c r="F958" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="959">
@@ -27269,7 +27269,7 @@
         </is>
       </c>
       <c r="F959" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="960">
@@ -27297,7 +27297,7 @@
         </is>
       </c>
       <c r="F960" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
     </row>
     <row r="961">
@@ -27353,7 +27353,7 @@
         </is>
       </c>
       <c r="F962" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="963">
@@ -27381,7 +27381,7 @@
         </is>
       </c>
       <c r="F963" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="964">
@@ -27409,7 +27409,7 @@
         </is>
       </c>
       <c r="F964" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="965">
@@ -27437,7 +27437,7 @@
         </is>
       </c>
       <c r="F965" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="966">
@@ -27465,7 +27465,7 @@
         </is>
       </c>
       <c r="F966" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="967">
@@ -27493,7 +27493,7 @@
         </is>
       </c>
       <c r="F967" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="968">
@@ -27605,7 +27605,7 @@
         </is>
       </c>
       <c r="F971" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="972">
@@ -27633,7 +27633,7 @@
         </is>
       </c>
       <c r="F972" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="973">
@@ -27689,7 +27689,7 @@
         </is>
       </c>
       <c r="F974" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="975">
@@ -27717,7 +27717,7 @@
         </is>
       </c>
       <c r="F975" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="976">
@@ -27745,7 +27745,7 @@
         </is>
       </c>
       <c r="F976" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="977">
@@ -27773,7 +27773,7 @@
         </is>
       </c>
       <c r="F977" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="978">
@@ -27801,7 +27801,7 @@
         </is>
       </c>
       <c r="F978" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="979">
@@ -27829,7 +27829,7 @@
         </is>
       </c>
       <c r="F979" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="980">
@@ -27857,7 +27857,7 @@
         </is>
       </c>
       <c r="F980" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="981">
@@ -27885,7 +27885,7 @@
         </is>
       </c>
       <c r="F981" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="982">
@@ -27913,7 +27913,7 @@
         </is>
       </c>
       <c r="F982" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="983">
@@ -27941,7 +27941,7 @@
         </is>
       </c>
       <c r="F983" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="984">
@@ -27997,7 +27997,7 @@
         </is>
       </c>
       <c r="F985" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="986">
@@ -28025,7 +28025,7 @@
         </is>
       </c>
       <c r="F986" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="987">
@@ -28053,7 +28053,7 @@
         </is>
       </c>
       <c r="F987" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="988">
@@ -28081,7 +28081,7 @@
         </is>
       </c>
       <c r="F988" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="989">
@@ -28109,7 +28109,7 @@
         </is>
       </c>
       <c r="F989" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="990">
@@ -28137,7 +28137,7 @@
         </is>
       </c>
       <c r="F990" t="n">
-        <v>-1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="991">
@@ -28165,7 +28165,7 @@
         </is>
       </c>
       <c r="F991" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="992">
@@ -28193,7 +28193,7 @@
         </is>
       </c>
       <c r="F992" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="993">
@@ -28221,7 +28221,7 @@
         </is>
       </c>
       <c r="F993" t="n">
-        <v>-1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="994">
@@ -28249,7 +28249,7 @@
         </is>
       </c>
       <c r="F994" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="995">
@@ -28277,7 +28277,7 @@
         </is>
       </c>
       <c r="F995" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="996">
@@ -28305,7 +28305,7 @@
         </is>
       </c>
       <c r="F996" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="997">
@@ -28333,7 +28333,7 @@
         </is>
       </c>
       <c r="F997" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="998">
@@ -28361,7 +28361,7 @@
         </is>
       </c>
       <c r="F998" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="999">
@@ -28389,7 +28389,7 @@
         </is>
       </c>
       <c r="F999" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1000">
@@ -28417,7 +28417,7 @@
         </is>
       </c>
       <c r="F1000" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1001">
@@ -28445,7 +28445,7 @@
         </is>
       </c>
       <c r="F1001" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
